--- a/SLR/Full-Paper-Read/Links-challenges.xlsx
+++ b/SLR/Full-Paper-Read/Links-challenges.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vitto\Desktop\github\SECO-for-CPS-Development-Study\SLR\Full-Paper-Read\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57753EC3-FCCD-4D68-9046-A620E68595E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA08695-DAC2-4437-AE40-2D5D5FEF77FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4269FE39-D5EE-416E-BEFD-A79E95E7D143}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4269FE39-D5EE-416E-BEFD-A79E95E7D143}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -246,7 +246,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,6 +262,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -293,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -301,29 +325,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,482 +743,482 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="87.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="9" t="s">
+      <c r="G3" s="9"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="10" t="s">
+      <c r="L3" s="12"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="11"/>
     </row>
-    <row r="4" spans="1:18" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
+    <row r="4" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
       <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="9" t="s">
+      <c r="F4" s="7"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
     </row>
-    <row r="5" spans="1:18" ht="88.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
+    <row r="5" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
       <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="9" t="s">
+      <c r="E5" s="9"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="9" t="s">
+      <c r="J5" s="12"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="10" t="s">
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
+    <row r="6" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
       <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="8"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="7"/>
       <c r="I6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="9" t="s">
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="12"/>
+      <c r="R6" s="10"/>
     </row>
-    <row r="7" spans="1:18" ht="61.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
+    <row r="7" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
       <c r="B7" s="2">
         <v>5</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="5"/>
+      <c r="D7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="9" t="s">
+      <c r="E7" s="8"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12" t="s">
         <v>46</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="9" t="s">
+      <c r="I7" s="7"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="11"/>
     </row>
-    <row r="8" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
+    <row r="8" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
       <c r="B8" s="2">
         <v>6</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="5"/>
+      <c r="D8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="9" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="9" t="s">
+      <c r="I8" s="10"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
     </row>
-    <row r="9" spans="1:18" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
+    <row r="9" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
       <c r="B9" s="2">
         <v>7</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="5"/>
+      <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="9" t="s">
+      <c r="F9" s="11"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="9" t="s">
+      <c r="N9" s="10"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="R9" s="5"/>
+      <c r="R9" s="10"/>
     </row>
-    <row r="10" spans="1:18" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
+    <row r="10" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
       <c r="B10" s="2">
         <v>8</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="4" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="9" t="s">
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="L10" s="8"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="9" t="s">
+      <c r="L10" s="7"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="R10" s="5"/>
+      <c r="R10" s="12"/>
     </row>
-    <row r="11" spans="1:18" ht="76.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
+    <row r="11" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
       <c r="B11" s="2">
         <v>9</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="9" t="s">
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="5"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="10" t="s">
+      <c r="L11" s="10"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
     </row>
-    <row r="12" spans="1:18" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
+    <row r="12" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
       <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="5"/>
+      <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="9" t="s">
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="10" t="s">
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="N12" s="8"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="12"/>
     </row>
-    <row r="13" spans="1:18" ht="73.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
+    <row r="13" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
       <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="9" t="s">
+      <c r="E13" s="11"/>
+      <c r="F13" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="9" t="s">
+      <c r="G13" s="8"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="10" t="s">
+      <c r="L13" s="12"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="R13" s="5"/>
+      <c r="R13" s="11"/>
     </row>
-    <row r="14" spans="1:18" ht="87" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
+    <row r="14" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
       <c r="B14" s="2">
         <v>12</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="4" t="s">
+      <c r="C14" s="5"/>
+      <c r="D14" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
       <c r="O14" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="9" t="s">
+      <c r="P14" s="7"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="73.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
+    <row r="15" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
       <c r="B15" s="2">
         <v>13</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="9" t="s">
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="10" t="s">
+      <c r="M15" s="11"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="5"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="11"/>
     </row>
-    <row r="16" spans="1:18" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
+    <row r="16" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
       <c r="B16" s="2">
         <v>14</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="10" t="s">
+      <c r="E16" s="11"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="5"/>
-      <c r="I16" s="9" t="s">
+      <c r="H16" s="10"/>
+      <c r="I16" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="8"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1212,6 +1242,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="05ea3171-6dd1-4eb8-abd1-6ce73298154c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d6a5746c-0d3c-4dee-a5cb-3134dcf3b5c6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="dokument" ma:contentTypeID="0x0101001D7F091B491B7C49A77745BFC21EE1DC" ma:contentTypeVersion="18" ma:contentTypeDescription="Skapa ett nytt dokument." ma:contentTypeScope="" ma:versionID="4235ce06c016ab017b311a59c6f61603">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d6a5746c-0d3c-4dee-a5cb-3134dcf3b5c6" xmlns:ns3="05ea3171-6dd1-4eb8-abd1-6ce73298154c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ff975443bb815c24b524641099939578" ns2:_="" ns3:_="">
     <xsd:import namespace="d6a5746c-0d3c-4dee-a5cb-3134dcf3b5c6"/>
@@ -1466,17 +1507,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="05ea3171-6dd1-4eb8-abd1-6ce73298154c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d6a5746c-0d3c-4dee-a5cb-3134dcf3b5c6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{91CB0B37-A48E-4F93-941D-65A965AAA487}">
   <ds:schemaRefs>
@@ -1486,6 +1516,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30D059A8-6D9F-42F7-AF58-D40217659A74}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="05ea3171-6dd1-4eb8-abd1-6ce73298154c"/>
+    <ds:schemaRef ds:uri="d6a5746c-0d3c-4dee-a5cb-3134dcf3b5c6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4A52941-5305-4438-9573-14E22C686212}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1502,15 +1543,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30D059A8-6D9F-42F7-AF58-D40217659A74}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="05ea3171-6dd1-4eb8-abd1-6ce73298154c"/>
-    <ds:schemaRef ds:uri="d6a5746c-0d3c-4dee-a5cb-3134dcf3b5c6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>